--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:18:10+00:00</t>
+    <t>2023-04-28T11:24:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:11+00:00</t>
+    <t>2023-04-28T11:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:31+00:00</t>
+    <t>2023-04-30T03:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:40+00:00</t>
+    <t>2023-04-30T03:44:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:58+00:00</t>
+    <t>2023-04-30T03:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:52:18+00:00</t>
+    <t>2023-04-30T03:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:53:51+00:00</t>
+    <t>2023-04-30T09:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T09:28:44+00:00</t>
+    <t>2023-05-01T08:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:52:03+00:00</t>
+    <t>2023-05-01T08:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:56:42+00:00</t>
+    <t>2023-05-01T09:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:10:15+00:00</t>
+    <t>2023-05-01T09:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:11:26+00:00</t>
+    <t>2023-05-01T09:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:13:53+00:00</t>
+    <t>2023-05-01T09:16:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:16:45+00:00</t>
+    <t>2023-05-01T16:40:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:06+00:00</t>
+    <t>2023-05-01T16:40:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:27+00:00</t>
+    <t>2023-05-01T18:12:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:00+00:00</t>
+    <t>2023-05-01T18:12:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:07+00:00</t>
+    <t>2023-05-02T21:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:23:22+00:00</t>
+    <t>2023-05-02T21:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:27:47+00:00</t>
+    <t>2023-05-03T08:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:35:52+00:00</t>
+    <t>2023-05-03T08:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:46:45+00:00</t>
+    <t>2023-05-03T08:57:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:04+00:00</t>
+    <t>2023-05-03T08:57:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:52+00:00</t>
+    <t>2023-05-04T12:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:38:34+00:00</t>
+    <t>2023-05-04T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:42:53+00:00</t>
+    <t>2023-05-05T21:01:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-07T12:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:05:50+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:13+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -872,7 +872,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/identifier/app-sample-id</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/identifier/app-sample-code</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1024,7 +1024,7 @@
     <t>Specimen.identifier:remoteSampleCode.system</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/identifier/remote-sample-id</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/identifier/remote-sample-code</t>
   </si>
   <si>
     <t>Specimen.identifier:remoteSampleCode.value</t>
@@ -1093,7 +1093,7 @@
     <t>Specimen.identifier:sampleCode.system</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/identifier/sample-id</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/identifier/sample-code</t>
   </si>
   <si>
     <t>Specimen.identifier:sampleCode.value</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4084" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4078" uniqueCount="556">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -268,6 +268,9 @@
     <t>Role[classCode=SPEC]</t>
   </si>
   <si>
+    <t>clinical.diagnostics</t>
+  </si>
+  <si>
     <t>Specimen.id</t>
   </si>
   <si>
@@ -351,7 +354,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -409,6 +412,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -459,6 +466,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Specimen.modifierExtension</t>
   </si>
   <si>
@@ -476,7 +487,7 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -526,201 +537,195 @@
     <t>Specimen.identifier.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Specimen.identifier:appSampleCode.extension</t>
+  </si>
+  <si>
+    <t>Specimen.identifier.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Specimen.identifier:appSampleCode.use</t>
+  </si>
+  <si>
+    <t>Specimen.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Specimen.identifier:appSampleCode.type</t>
+  </si>
+  <si>
+    <t>Specimen.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Specimen.identifier:appSampleCode.type.id</t>
+  </si>
+  <si>
+    <t>Specimen.identifier.type.id</t>
+  </si>
+  <si>
+    <t>Specimen.identifier:appSampleCode.type.extension</t>
+  </si>
+  <si>
+    <t>Specimen.identifier.type.extension</t>
+  </si>
+  <si>
+    <t>Specimen.identifier:appSampleCode.type.coding</t>
+  </si>
+  <si>
+    <t>Specimen.identifier.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Specimen.identifier:appSampleCode.type.coding.id</t>
+  </si>
+  <si>
+    <t>Specimen.identifier.type.coding.id</t>
+  </si>
+  <si>
+    <t>Specimen.identifier:appSampleCode.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Specimen.identifier.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Specimen.identifier:appSampleCode.type.coding.system</t>
+  </si>
+  <si>
+    <t>Specimen.identifier.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Specimen.identifier:appSampleCode.type.coding.version</t>
+  </si>
+  <si>
+    <t>Specimen.identifier.type.coding.version</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Specimen.identifier:appSampleCode.extension</t>
-  </si>
-  <si>
-    <t>Specimen.identifier.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Specimen.identifier:appSampleCode.use</t>
-  </si>
-  <si>
-    <t>Specimen.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Specimen.identifier:appSampleCode.type</t>
-  </si>
-  <si>
-    <t>Specimen.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Specimen.identifier:appSampleCode.type.id</t>
-  </si>
-  <si>
-    <t>Specimen.identifier.type.id</t>
-  </si>
-  <si>
-    <t>Specimen.identifier:appSampleCode.type.extension</t>
-  </si>
-  <si>
-    <t>Specimen.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>Specimen.identifier:appSampleCode.type.coding</t>
-  </si>
-  <si>
-    <t>Specimen.identifier.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>Specimen.identifier:appSampleCode.type.coding.id</t>
-  </si>
-  <si>
-    <t>Specimen.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>Specimen.identifier:appSampleCode.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Specimen.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Specimen.identifier:appSampleCode.type.coding.system</t>
-  </si>
-  <si>
-    <t>Specimen.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>Specimen.identifier:appSampleCode.type.coding.version</t>
-  </si>
-  <si>
-    <t>Specimen.identifier.type.coding.version</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -899,7 +904,7 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -1135,7 +1140,7 @@
     <t>Codes providing the status/availability of a specimen.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-status|4.3.0</t>
   </si>
   <si>
     <t>status</t>
@@ -1435,10 +1440,10 @@
     <t>Anatomical location from which the specimen was collected (if subject is a patient). This is the target site.  This element is not used for environmental specimens.</t>
   </si>
   <si>
-    <t>If the use case requires  BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
+    <t>If the use case requires  BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1485,6 +1490,10 @@
   </si>
   <si>
     <t>Details concerning processing and processing steps for the specimen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].act[code=SPCTRT, moodCode=EVN]</t>
@@ -2062,7 +2071,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="57.1484375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="57.9296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -2300,7 +2309,7 @@
         <v>82</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>76</v>
@@ -2308,10 +2317,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2322,7 +2331,7 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>76</v>
@@ -2331,19 +2340,19 @@
         <v>76</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2393,13 +2402,13 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>76</v>
@@ -2419,10 +2428,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2433,7 +2442,7 @@
         <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>76</v>
@@ -2442,16 +2451,16 @@
         <v>76</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2502,19 +2511,19 @@
         <v>76</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
@@ -2528,10 +2537,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2542,28 +2551,28 @@
         <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2613,19 +2622,19 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>76</v>
@@ -2639,10 +2648,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2653,7 +2662,7 @@
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -2665,16 +2674,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2700,13 +2709,13 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>76</v>
@@ -2724,19 +2733,19 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>76</v>
@@ -2750,21 +2759,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>76</v>
@@ -2776,16 +2785,16 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2835,22 +2844,22 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>76</v>
@@ -2861,14 +2870,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2887,16 +2896,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2946,7 +2955,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2958,10 +2967,10 @@
         <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>76</v>
@@ -2972,10 +2981,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2998,13 +3007,13 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3043,17 +3052,17 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -3065,7 +3074,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -3079,13 +3088,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>76</v>
@@ -3095,10 +3104,10 @@
         <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>76</v>
@@ -3107,13 +3116,13 @@
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3164,7 +3173,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -3173,10 +3182,10 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -3190,14 +3199,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3210,25 +3219,25 @@
         <v>76</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -3277,7 +3286,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -3289,10 +3298,10 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>76</v>
@@ -3303,10 +3312,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3314,7 +3323,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>78</v>
@@ -3326,16 +3335,16 @@
         <v>76</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3374,17 +3383,17 @@
         <v>76</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -3396,37 +3405,37 @@
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>76</v>
@@ -3435,16 +3444,16 @@
         <v>76</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3495,7 +3504,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3507,24 +3516,24 @@
         <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3535,7 +3544,7 @@
         <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>76</v>
@@ -3547,13 +3556,13 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3604,13 +3613,13 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>76</v>
@@ -3619,7 +3628,7 @@
         <v>76</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>76</v>
@@ -3630,14 +3639,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3656,16 +3665,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3703,19 +3712,19 @@
         <v>76</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3727,10 +3736,10 @@
         <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>76</v>
@@ -3741,10 +3750,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3755,31 +3764,31 @@
         <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -3804,13 +3813,11 @@
         <v>76</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>76</v>
@@ -3828,36 +3835,36 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3868,7 +3875,7 @@
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>76</v>
@@ -3877,22 +3884,22 @@
         <v>76</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3917,11 +3924,9 @@
         <v>76</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y17" t="s" s="2">
         <v>193</v>
       </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
         <v>194</v>
       </c>
@@ -3947,16 +3952,16 @@
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3981,7 +3986,7 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>76</v>
@@ -3993,13 +3998,13 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4050,13 +4055,13 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>76</v>
@@ -4065,7 +4070,7 @@
         <v>76</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
@@ -4083,7 +4088,7 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4102,16 +4107,16 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4149,19 +4154,19 @@
         <v>76</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -4173,10 +4178,10 @@
         <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>76</v>
@@ -4210,7 +4215,7 @@
         <v>76</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>203</v>
@@ -4286,7 +4291,7 @@
         <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>209</v>
@@ -4314,7 +4319,7 @@
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>76</v>
@@ -4326,13 +4331,13 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4383,13 +4388,13 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>76</v>
@@ -4398,7 +4403,7 @@
         <v>76</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
@@ -4416,7 +4421,7 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4435,16 +4440,16 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4482,19 +4487,19 @@
         <v>76</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4506,10 +4511,10 @@
         <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
@@ -4534,7 +4539,7 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>76</v>
@@ -4543,10 +4548,10 @@
         <v>76</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>217</v>
@@ -4613,13 +4618,13 @@
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>223</v>
@@ -4647,7 +4652,7 @@
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>76</v>
@@ -4656,19 +4661,19 @@
         <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4718,36 +4723,36 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4758,7 +4763,7 @@
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>76</v>
@@ -4767,20 +4772,20 @@
         <v>76</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4790,7 +4795,7 @@
         <v>76</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>76</v>
@@ -4829,36 +4834,36 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4869,7 +4874,7 @@
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>76</v>
@@ -4878,20 +4883,20 @@
         <v>76</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4901,7 +4906,7 @@
         <v>76</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>76</v>
@@ -4940,36 +4945,36 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4980,7 +4985,7 @@
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>76</v>
@@ -4989,22 +4994,22 @@
         <v>76</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -5053,36 +5058,36 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5093,7 +5098,7 @@
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -5102,22 +5107,22 @@
         <v>76</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -5127,7 +5132,7 @@
         <v>76</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>76</v>
@@ -5166,36 +5171,36 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5203,10 +5208,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>76</v>
@@ -5215,35 +5220,35 @@
         <v>76</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>76</v>
@@ -5279,36 +5284,36 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5316,10 +5321,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>76</v>
@@ -5328,19 +5333,19 @@
         <v>76</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5354,7 +5359,7 @@
         <v>76</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>76</v>
@@ -5390,36 +5395,36 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5430,7 +5435,7 @@
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>76</v>
@@ -5439,16 +5444,16 @@
         <v>76</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5499,36 +5504,36 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5539,7 +5544,7 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>76</v>
@@ -5548,19 +5553,19 @@
         <v>76</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5610,49 +5615,49 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>76</v>
@@ -5661,16 +5666,16 @@
         <v>76</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5721,7 +5726,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5733,24 +5738,24 @@
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5761,7 +5766,7 @@
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>76</v>
@@ -5773,13 +5778,13 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5830,13 +5835,13 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>76</v>
@@ -5845,7 +5850,7 @@
         <v>76</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5856,14 +5861,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5882,16 +5887,16 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5929,19 +5934,19 @@
         <v>76</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5953,10 +5958,10 @@
         <v>76</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
@@ -5967,10 +5972,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5981,31 +5986,31 @@
         <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>76</v>
@@ -6030,13 +6035,11 @@
         <v>76</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>76</v>
@@ -6054,36 +6057,36 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6094,7 +6097,7 @@
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>76</v>
@@ -6103,22 +6106,22 @@
         <v>76</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -6143,11 +6146,9 @@
         <v>76</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y37" t="s" s="2">
         <v>193</v>
       </c>
+      <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
         <v>194</v>
       </c>
@@ -6173,16 +6174,16 @@
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -6193,7 +6194,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>198</v>
@@ -6207,7 +6208,7 @@
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>76</v>
@@ -6219,13 +6220,13 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6276,13 +6277,13 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>76</v>
@@ -6291,7 +6292,7 @@
         <v>76</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -6302,14 +6303,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6328,16 +6329,16 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6375,19 +6376,19 @@
         <v>76</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6399,10 +6400,10 @@
         <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>76</v>
@@ -6413,7 +6414,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>202</v>
@@ -6436,7 +6437,7 @@
         <v>76</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>203</v>
@@ -6512,7 +6513,7 @@
         <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>209</v>
@@ -6526,7 +6527,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>212</v>
@@ -6540,7 +6541,7 @@
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>76</v>
@@ -6552,13 +6553,13 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6609,13 +6610,13 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>76</v>
@@ -6624,7 +6625,7 @@
         <v>76</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>76</v>
@@ -6635,14 +6636,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>214</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6661,16 +6662,16 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6708,19 +6709,19 @@
         <v>76</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6732,10 +6733,10 @@
         <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
@@ -6746,7 +6747,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>216</v>
@@ -6760,7 +6761,7 @@
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>76</v>
@@ -6769,10 +6770,10 @@
         <v>76</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>217</v>
@@ -6839,13 +6840,13 @@
         <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>223</v>
@@ -6859,7 +6860,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>226</v>
@@ -6873,7 +6874,7 @@
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>76</v>
@@ -6882,19 +6883,19 @@
         <v>76</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6944,36 +6945,36 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6984,7 +6985,7 @@
         <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>76</v>
@@ -6993,20 +6994,20 @@
         <v>76</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>76</v>
@@ -7016,7 +7017,7 @@
         <v>76</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>76</v>
@@ -7055,36 +7056,36 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7095,7 +7096,7 @@
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>76</v>
@@ -7104,20 +7105,20 @@
         <v>76</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -7127,7 +7128,7 @@
         <v>76</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>76</v>
@@ -7166,36 +7167,36 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7206,7 +7207,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>76</v>
@@ -7215,22 +7216,22 @@
         <v>76</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -7279,36 +7280,36 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7319,7 +7320,7 @@
         <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>76</v>
@@ -7328,22 +7329,22 @@
         <v>76</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -7353,7 +7354,7 @@
         <v>76</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>76</v>
@@ -7392,36 +7393,36 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7429,10 +7430,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>76</v>
@@ -7441,35 +7442,35 @@
         <v>76</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>76</v>
@@ -7505,36 +7506,36 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7542,10 +7543,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>76</v>
@@ -7554,19 +7555,19 @@
         <v>76</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7580,7 +7581,7 @@
         <v>76</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>76</v>
@@ -7616,36 +7617,36 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7656,7 +7657,7 @@
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>76</v>
@@ -7665,16 +7666,16 @@
         <v>76</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7725,36 +7726,36 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7765,7 +7766,7 @@
         <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>76</v>
@@ -7774,19 +7775,19 @@
         <v>76</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7836,49 +7837,49 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>76</v>
@@ -7887,16 +7888,16 @@
         <v>76</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7947,7 +7948,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7959,24 +7960,24 @@
         <v>76</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7987,7 +7988,7 @@
         <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>76</v>
@@ -7999,13 +8000,13 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8056,13 +8057,13 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>76</v>
@@ -8071,7 +8072,7 @@
         <v>76</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>76</v>
@@ -8082,14 +8083,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8108,16 +8109,16 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8155,19 +8156,19 @@
         <v>76</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8179,10 +8180,10 @@
         <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
@@ -8193,10 +8194,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8207,31 +8208,31 @@
         <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -8256,13 +8257,11 @@
         <v>76</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>76</v>
@@ -8280,36 +8279,36 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8320,7 +8319,7 @@
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>76</v>
@@ -8329,22 +8328,22 @@
         <v>76</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -8369,11 +8368,9 @@
         <v>76</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y57" t="s" s="2">
         <v>193</v>
       </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
         <v>194</v>
       </c>
@@ -8399,16 +8396,16 @@
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>76</v>
@@ -8419,7 +8416,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>198</v>
@@ -8433,7 +8430,7 @@
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>76</v>
@@ -8445,13 +8442,13 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8502,13 +8499,13 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>76</v>
@@ -8517,7 +8514,7 @@
         <v>76</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>76</v>
@@ -8528,14 +8525,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8554,16 +8551,16 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8601,19 +8598,19 @@
         <v>76</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8625,10 +8622,10 @@
         <v>76</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>76</v>
@@ -8639,7 +8636,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>202</v>
@@ -8662,7 +8659,7 @@
         <v>76</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>203</v>
@@ -8738,7 +8735,7 @@
         <v>76</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>209</v>
@@ -8752,7 +8749,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>212</v>
@@ -8766,7 +8763,7 @@
         <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>76</v>
@@ -8778,13 +8775,13 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8835,13 +8832,13 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>76</v>
@@ -8850,7 +8847,7 @@
         <v>76</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>76</v>
@@ -8861,14 +8858,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>214</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8887,16 +8884,16 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8934,19 +8931,19 @@
         <v>76</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8958,10 +8955,10 @@
         <v>76</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>76</v>
@@ -8972,7 +8969,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>216</v>
@@ -8986,7 +8983,7 @@
         <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>76</v>
@@ -8995,10 +8992,10 @@
         <v>76</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>217</v>
@@ -9065,13 +9062,13 @@
         <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>223</v>
@@ -9085,7 +9082,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>226</v>
@@ -9099,7 +9096,7 @@
         <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>76</v>
@@ -9108,19 +9105,19 @@
         <v>76</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9170,36 +9167,36 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9210,7 +9207,7 @@
         <v>77</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>76</v>
@@ -9219,20 +9216,20 @@
         <v>76</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
@@ -9242,7 +9239,7 @@
         <v>76</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>76</v>
@@ -9281,36 +9278,36 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9321,7 +9318,7 @@
         <v>77</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>76</v>
@@ -9330,20 +9327,20 @@
         <v>76</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -9353,7 +9350,7 @@
         <v>76</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>76</v>
@@ -9392,36 +9389,36 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9432,7 +9429,7 @@
         <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>76</v>
@@ -9441,22 +9438,22 @@
         <v>76</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>76</v>
@@ -9505,36 +9502,36 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9545,7 +9542,7 @@
         <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>76</v>
@@ -9554,22 +9551,22 @@
         <v>76</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>76</v>
@@ -9579,7 +9576,7 @@
         <v>76</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>76</v>
@@ -9618,36 +9615,36 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9655,10 +9652,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>76</v>
@@ -9667,35 +9664,35 @@
         <v>76</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>76</v>
@@ -9731,36 +9728,36 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9768,10 +9765,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>76</v>
@@ -9780,19 +9777,19 @@
         <v>76</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9806,7 +9803,7 @@
         <v>76</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>76</v>
@@ -9842,36 +9839,36 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9882,7 +9879,7 @@
         <v>77</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>76</v>
@@ -9891,16 +9888,16 @@
         <v>76</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9951,36 +9948,36 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9991,7 +9988,7 @@
         <v>77</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>76</v>
@@ -10000,19 +9997,19 @@
         <v>76</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10062,36 +10059,36 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10102,7 +10099,7 @@
         <v>77</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>76</v>
@@ -10111,16 +10108,16 @@
         <v>76</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10171,36 +10168,36 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10211,28 +10208,28 @@
         <v>77</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10258,13 +10255,13 @@
         <v>76</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>76</v>
@@ -10282,36 +10279,36 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10319,10 +10316,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>76</v>
@@ -10331,19 +10328,19 @@
         <v>76</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10369,11 +10366,11 @@
         <v>76</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>76</v>
@@ -10391,36 +10388,36 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10431,7 +10428,7 @@
         <v>77</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>76</v>
@@ -10443,13 +10440,13 @@
         <v>76</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10500,13 +10497,13 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>76</v>
@@ -10515,7 +10512,7 @@
         <v>76</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>76</v>
@@ -10526,14 +10523,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10552,16 +10549,16 @@
         <v>76</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10599,19 +10596,19 @@
         <v>76</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10623,10 +10620,10 @@
         <v>76</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>76</v>
@@ -10637,10 +10634,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10660,7 +10657,7 @@
         <v>76</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>203</v>
@@ -10736,7 +10733,7 @@
         <v>76</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>209</v>
@@ -10750,10 +10747,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10764,7 +10761,7 @@
         <v>77</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>76</v>
@@ -10773,22 +10770,22 @@
         <v>76</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>76</v>
@@ -10798,7 +10795,7 @@
         <v>76</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>76</v>
@@ -10837,36 +10834,36 @@
         <v>76</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10874,10 +10871,10 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>76</v>
@@ -10886,20 +10883,20 @@
         <v>76</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>76</v>
@@ -10948,25 +10945,25 @@
         <v>76</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>76</v>
@@ -10974,10 +10971,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10988,25 +10985,25 @@
         <v>77</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11057,36 +11054,36 @@
         <v>76</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11109,16 +11106,16 @@
         <v>76</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11168,7 +11165,7 @@
         <v>76</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -11180,10 +11177,10 @@
         <v>76</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>76</v>
@@ -11194,10 +11191,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11220,16 +11217,16 @@
         <v>76</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11279,7 +11276,7 @@
         <v>76</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11291,24 +11288,24 @@
         <v>76</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11319,7 +11316,7 @@
         <v>77</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>76</v>
@@ -11331,13 +11328,13 @@
         <v>76</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11388,13 +11385,13 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>76</v>
@@ -11403,21 +11400,21 @@
         <v>76</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11428,7 +11425,7 @@
         <v>77</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>76</v>
@@ -11440,13 +11437,13 @@
         <v>76</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11497,13 +11494,13 @@
         <v>76</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>76</v>
@@ -11512,7 +11509,7 @@
         <v>76</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>76</v>
@@ -11523,14 +11520,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -11549,16 +11546,16 @@
         <v>76</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11608,7 +11605,7 @@
         <v>76</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -11620,10 +11617,10 @@
         <v>76</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>76</v>
@@ -11634,14 +11631,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -11654,25 +11651,25 @@
         <v>76</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>76</v>
@@ -11721,7 +11718,7 @@
         <v>76</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
@@ -11733,10 +11730,10 @@
         <v>76</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>76</v>
@@ -11747,10 +11744,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11761,7 +11758,7 @@
         <v>77</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>76</v>
@@ -11770,16 +11767,16 @@
         <v>76</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11830,36 +11827,36 @@
         <v>76</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11870,7 +11867,7 @@
         <v>77</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>76</v>
@@ -11879,16 +11876,16 @@
         <v>76</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11927,49 +11924,49 @@
         <v>76</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>76</v>
@@ -11979,25 +11976,25 @@
         <v>77</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12048,36 +12045,36 @@
         <v>76</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12088,7 +12085,7 @@
         <v>77</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>76</v>
@@ -12097,16 +12094,16 @@
         <v>76</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12157,25 +12154,25 @@
         <v>76</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>76</v>
@@ -12183,10 +12180,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12197,7 +12194,7 @@
         <v>77</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>76</v>
@@ -12209,13 +12206,13 @@
         <v>76</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12266,36 +12263,36 @@
         <v>76</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12306,7 +12303,7 @@
         <v>77</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>76</v>
@@ -12318,13 +12315,13 @@
         <v>76</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12351,13 +12348,13 @@
         <v>76</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>76</v>
@@ -12375,36 +12372,36 @@
         <v>76</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12415,7 +12412,7 @@
         <v>77</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>76</v>
@@ -12427,16 +12424,16 @@
         <v>76</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12462,13 +12459,13 @@
         <v>76</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>76</v>
@@ -12486,36 +12483,36 @@
         <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12526,7 +12523,7 @@
         <v>77</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>76</v>
@@ -12535,22 +12532,22 @@
         <v>76</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>76</v>
@@ -12575,13 +12572,13 @@
         <v>76</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>76</v>
@@ -12599,19 +12596,19 @@
         <v>76</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>76</v>
@@ -12620,15 +12617,15 @@
         <v>76</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12639,10 +12636,10 @@
         <v>77</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>76</v>
@@ -12651,13 +12648,13 @@
         <v>76</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12708,7 +12705,7 @@
         <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
@@ -12720,10 +12717,10 @@
         <v>76</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>96</v>
+        <v>478</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>76</v>
@@ -12734,10 +12731,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12748,7 +12745,7 @@
         <v>77</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>76</v>
@@ -12760,13 +12757,13 @@
         <v>76</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -12817,13 +12814,13 @@
         <v>76</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>76</v>
@@ -12832,7 +12829,7 @@
         <v>76</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>76</v>
@@ -12843,14 +12840,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -12869,16 +12866,16 @@
         <v>76</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -12928,7 +12925,7 @@
         <v>76</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
@@ -12940,10 +12937,10 @@
         <v>76</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>76</v>
@@ -12954,14 +12951,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -12974,25 +12971,25 @@
         <v>76</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>76</v>
@@ -13041,7 +13038,7 @@
         <v>76</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -13053,10 +13050,10 @@
         <v>76</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>76</v>
@@ -13067,10 +13064,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13081,7 +13078,7 @@
         <v>77</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>76</v>
@@ -13093,13 +13090,13 @@
         <v>76</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13150,22 +13147,22 @@
         <v>76</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>76</v>
@@ -13176,10 +13173,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13190,7 +13187,7 @@
         <v>77</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>76</v>
@@ -13202,13 +13199,13 @@
         <v>76</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13235,13 +13232,13 @@
         <v>76</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>76</v>
@@ -13259,22 +13256,22 @@
         <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>76</v>
@@ -13285,10 +13282,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13311,13 +13308,13 @@
         <v>76</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13368,7 +13365,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -13380,24 +13377,24 @@
         <v>76</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13405,10 +13402,10 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>76</v>
@@ -13420,13 +13417,13 @@
         <v>76</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13465,32 +13462,32 @@
         <v>76</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>76</v>
@@ -13501,23 +13498,23 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>76</v>
@@ -13529,13 +13526,13 @@
         <v>76</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13586,22 +13583,22 @@
         <v>76</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>76</v>
@@ -13612,10 +13609,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13638,13 +13635,13 @@
         <v>76</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13695,7 +13692,7 @@
         <v>76</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
@@ -13707,10 +13704,10 @@
         <v>76</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>96</v>
+        <v>478</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>76</v>
@@ -13721,10 +13718,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13735,7 +13732,7 @@
         <v>77</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>76</v>
@@ -13747,13 +13744,13 @@
         <v>76</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -13804,13 +13801,13 @@
         <v>76</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>76</v>
@@ -13819,7 +13816,7 @@
         <v>76</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>76</v>
@@ -13830,14 +13827,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13856,16 +13853,16 @@
         <v>76</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -13915,7 +13912,7 @@
         <v>76</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
@@ -13927,10 +13924,10 @@
         <v>76</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>76</v>
@@ -13941,14 +13938,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -13961,25 +13958,25 @@
         <v>76</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>76</v>
@@ -14028,7 +14025,7 @@
         <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
@@ -14040,10 +14037,10 @@
         <v>76</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>76</v>
@@ -14054,10 +14051,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14077,16 +14074,16 @@
         <v>76</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14137,7 +14134,7 @@
         <v>76</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
@@ -14149,24 +14146,24 @@
         <v>76</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14177,7 +14174,7 @@
         <v>77</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>76</v>
@@ -14189,13 +14186,13 @@
         <v>76</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14246,22 +14243,22 @@
         <v>76</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>76</v>
@@ -14272,10 +14269,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14286,7 +14283,7 @@
         <v>77</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>76</v>
@@ -14298,13 +14295,13 @@
         <v>76</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14331,13 +14328,13 @@
         <v>76</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>76</v>
@@ -14355,36 +14352,36 @@
         <v>76</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14395,7 +14392,7 @@
         <v>77</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>76</v>
@@ -14407,13 +14404,13 @@
         <v>76</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14464,36 +14461,36 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14504,7 +14501,7 @@
         <v>77</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>76</v>
@@ -14516,13 +14513,13 @@
         <v>76</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14573,36 +14570,36 @@
         <v>76</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14613,7 +14610,7 @@
         <v>77</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>76</v>
@@ -14625,13 +14622,13 @@
         <v>76</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -14658,13 +14655,13 @@
         <v>76</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>76</v>
@@ -14682,36 +14679,36 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14731,22 +14728,22 @@
         <v>76</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>76</v>
@@ -14771,13 +14768,13 @@
         <v>76</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>76</v>
@@ -14795,7 +14792,7 @@
         <v>76</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -14807,7 +14804,7 @@
         <v>76</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>76</v>
@@ -14816,15 +14813,15 @@
         <v>76</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14838,7 +14835,7 @@
         <v>78</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>76</v>
@@ -14847,13 +14844,13 @@
         <v>76</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L116" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14904,7 +14901,7 @@
         <v>76</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
@@ -14916,16 +14913,16 @@
         <v>76</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
